--- a/mobility-data-standard/mobility-data-standard.xlsx
+++ b/mobility-data-standard/mobility-data-standard.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A306180-CE51-4CC9-B01E-A5B8FFE17F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138286F2-E46E-4CF2-8C66-EDEB33A95618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
+    <sheet name="Vocabulary" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,17 +36,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
   <si>
     <t>ConceptScheme URI</t>
   </si>
   <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard</t>
+  </si>
+  <si>
     <t>dct:title</t>
   </si>
   <si>
+    <t>Mobility data standard</t>
+  </si>
+  <si>
     <t>dct:description</t>
   </si>
   <si>
+    <t>Controlled vocabulary for the mobility data standard adopted by a distribution.</t>
+  </si>
+  <si>
     <t>dct:creator</t>
   </si>
   <si>
@@ -55,6 +65,12 @@
     <t>Peter Lubrich (BASt)</t>
   </si>
   <si>
+    <t>Ed Ooms (NDW)</t>
+  </si>
+  <si>
+    <t>Petr Bures (TamTam Research)</t>
+  </si>
+  <si>
     <t>dct:publisher</t>
   </si>
   <si>
@@ -67,16 +83,25 @@
     <t>owl:versionInfo</t>
   </si>
   <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>owl:versionIRI</t>
   </si>
   <si>
+    <t>owl:priorVersion</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.1.0</t>
+  </si>
+  <si>
     <t>dct:license</t>
   </si>
   <si>
     <t>https://creativecommons.org/licenses/by/4.0/</t>
   </si>
   <si>
-    <t>My comments (not parsed by the tool).</t>
+    <t>http://purl.org/ontology/bibo/status</t>
   </si>
   <si>
     <t>URI</t>
@@ -91,19 +116,199 @@
     <t>skos:narrower</t>
   </si>
   <si>
+    <t>rdf:type</t>
+  </si>
+  <si>
     <t>skos:notation</t>
   </si>
   <si>
-    <t>DATEX II (CEN/TS 16157)</t>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/apds</t>
+  </si>
+  <si>
+    <t>APDS</t>
+  </si>
+  <si>
+    <t>Alliance for Parking Data Standards (ADPS)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/alert-c</t>
+  </si>
+  <si>
+    <t>ALERT-C</t>
+  </si>
+  <si>
+    <t>Traffic Message Channel (TMC) ALERT‑C location table standard (CEN/EN 14819‑3)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/cds</t>
+  </si>
+  <si>
+    <t>CDS</t>
+  </si>
+  <si>
+    <t>Curb Data Specification (Open Mobility Foundation)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/cds-m</t>
+  </si>
+  <si>
+    <t>CDS-M</t>
+  </si>
+  <si>
+    <t>City Data Specification for Mobility (Open Mobility Foundation)</t>
+  </si>
+  <si>
+    <t>C-ITS</t>
+  </si>
+  <si>
+    <t>Cooperative ITS message standards: CAM (ETSI EN 302 637-2), DENM (ETSI EN 302 637-3), SPAT/MAP (SAE-J2735 and ISO 19091)</t>
+  </si>
+  <si>
+    <t>DATEX II</t>
+  </si>
+  <si>
+    <t>Road Traffic and Travel Data Exchange (DATEX II, CEN/TS 16157)</t>
+  </si>
+  <si>
+    <t>DINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DINO exchange format based on the VDV-DIVA exchange format </t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/e-cmr</t>
+  </si>
+  <si>
+    <t>e-CMR</t>
+  </si>
+  <si>
+    <t>Electronic Consignment Note under the UNECE CMR Convention</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/era</t>
+  </si>
+  <si>
+    <t>ERA Ontology</t>
+  </si>
+  <si>
+    <t>Ontology of the European Railway Agency (ERA)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ertms</t>
+  </si>
+  <si>
+    <t>ERTMS</t>
+  </si>
+  <si>
+    <t>European Rail Traffic Management System</t>
+  </si>
+  <si>
+    <t>GBFS</t>
+  </si>
+  <si>
+    <t>General Bikeshare Feed Specification (MobilityData)</t>
+  </si>
+  <si>
+    <t>GML</t>
+  </si>
+  <si>
+    <t>Geography Markup Language (OGC) XML encoding</t>
+  </si>
+  <si>
+    <t>GTFS</t>
+  </si>
+  <si>
+    <t>General Transit Feed Specification - Schedule (MobilityData)</t>
+  </si>
+  <si>
+    <t>GTFS-RT</t>
+  </si>
+  <si>
+    <t>General Transit Feed Specification - Realtime (MobilityData)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/inspire</t>
+  </si>
+  <si>
+    <t>INSPIRE DS TN</t>
+  </si>
+  <si>
+    <t>INSPIRE Data Specification on Transport Networks</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/mds</t>
+  </si>
+  <si>
+    <t>MDS</t>
+  </si>
+  <si>
+    <t>Mobility Data Specification (Open Mobility Foundation)</t>
+  </si>
+  <si>
+    <t>NeTEx</t>
+  </si>
+  <si>
+    <t>Network and Timetable Exchange (NeTEx, CEN/TS 16614)</t>
+  </si>
+  <si>
+    <t>OCIT-O</t>
+  </si>
+  <si>
+    <t>OCIT (Open Communication Interface for Road Traffic Control Systems) Outstations</t>
   </si>
   <si>
     <t>OCIT-C</t>
   </si>
   <si>
-    <t>C-ITS</t>
-  </si>
-  <si>
-    <t>CAM (ETSI EN 302 637-2), DENM (ETSI EN 302 637-3), SPAT/MAP (SAE-J2735 and ISO 19091)</t>
+    <t>OCIT (Open Communication Interface for Road Traffic Control Systems) Center-to-Center</t>
+  </si>
+  <si>
+    <t>OCPI</t>
+  </si>
+  <si>
+    <t>Open Charge Point Interface (OCPI)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ojp</t>
+  </si>
+  <si>
+    <t>OJP</t>
+  </si>
+  <si>
+    <t>Open Journey Planner (CEN/TS 17118)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/opentnf</t>
+  </si>
+  <si>
+    <t>OpenTNF</t>
+  </si>
+  <si>
+    <t>Open specification for interoperability and exchange of data on transport networks</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/opra</t>
+  </si>
+  <si>
+    <t>OpRa</t>
+  </si>
+  <si>
+    <t>Operating Raw Data and Statistics Exchange (CEN/TS 17413)</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/osdm</t>
+  </si>
+  <si>
+    <t>OSDM</t>
+  </si>
+  <si>
+    <t>Open Sales and Distribution Model (OSDM)</t>
+  </si>
+  <si>
+    <t>SIRI</t>
+  </si>
+  <si>
+    <t>Service Interface for Real‑time Information (SIRI, CEN/TS 15531)</t>
   </si>
   <si>
     <t>TN-ITS</t>
@@ -112,89 +317,31 @@
     <t>TN-ITS (CEN/TS 17268)</t>
   </si>
   <si>
-    <t>INSPIRE</t>
-  </si>
-  <si>
-    <t>D2.8.I.7 Data Specification on Transport Networks – Technical 
-Guidelines</t>
-  </si>
-  <si>
-    <t>GML</t>
-  </si>
-  <si>
-    <t>NeTEx</t>
-  </si>
-  <si>
-    <t>NeTEx (CEN/TS 16614)</t>
-  </si>
-  <si>
-    <t>SIRI</t>
-  </si>
-  <si>
-    <t>SIRI (CEN/TS 15531)</t>
-  </si>
-  <si>
-    <t>GTFS</t>
-  </si>
-  <si>
-    <t>GTFS-RT</t>
-  </si>
-  <si>
-    <t>GBFS</t>
+    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tomp-api</t>
+  </si>
+  <si>
+    <t>TOMP-API</t>
+  </si>
+  <si>
+    <t>Transport Operator - MaaS Provider API</t>
   </si>
   <si>
     <t>tpegML</t>
   </si>
   <si>
-    <t>DINO</t>
+    <t>XML encoding of TPEG messages (ISO/TS 21219 series)</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Mobility data standard</t>
-  </si>
-  <si>
-    <t>Controlled vocabulary for the mobility data standard adopted by a distribution.</t>
-  </si>
-  <si>
-    <t>DATEX II</t>
-  </si>
-  <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard</t>
-  </si>
-  <si>
-    <t>http://purl.org/ontology/bibo/status</t>
-  </si>
-  <si>
-    <t>owl:priorVersion</t>
-  </si>
-  <si>
-    <t>Published Controlled Vocabulary</t>
-  </si>
-  <si>
-    <t>Open Communication Interface for Road Traffic Control Systems</t>
-  </si>
-  <si>
-    <t>General Transit Feed Specification - Schedule</t>
-  </si>
-  <si>
-    <t>General Transit Feed Specification - Realtime</t>
-  </si>
-  <si>
-    <t>General Bikeshare Feed Specification</t>
-  </si>
-  <si>
-    <t>OCPI</t>
-  </si>
-  <si>
-    <t>Open Charge Point Interface (OCPI)</t>
-  </si>
-  <si>
-    <t>1.1.0</t>
-  </si>
-  <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.0.0</t>
+    <t>Dataset uses a data standard not listed in this vocabulary</t>
+  </si>
+  <si>
+    <t>Draft Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t>skos:Concept,https://w3id.org/mobilitydcatap#MobilityDataStandard</t>
   </si>
 </sst>
 </file>
@@ -232,7 +379,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +389,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -271,7 +430,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -282,7 +440,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -299,6 +484,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -587,444 +776,632 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="72.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="77.140625" customWidth="1"/>
     <col min="4" max="4" width="45.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" customWidth="1"/>
+    <col min="5" max="5" width="67.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>41</v>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B9)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.1.0</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B12" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B11)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.2.0</v>
       </c>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B23)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/c-its</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B24)," ","-"),",",""),"ii","II"))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C24" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B25)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/dino</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B19)," ","-"),",",""),"ii","II"))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="str">
-        <f t="shared" ref="A20:A33" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B20)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-c</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/c-its</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tn-its</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/inspire</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="str">
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f t="shared" ref="A29:A32" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B29)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gml</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/netex</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="str">
+      <c r="B30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="str">
+      <c r="B31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs-rt</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B29)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="str">
-        <f t="shared" si="0"/>
+      <c r="B32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B35)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/netex</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B36)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-o</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-c</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B38)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocpi</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B43)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B44)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tn-its</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B46)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tpegml</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="8"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/dino</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocpi</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="str">
-        <f t="shared" si="0"/>
+      <c r="B46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B47)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/other</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="7"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="7"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="7"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="7"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="7"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
+      <c r="B47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C46">
+    <sortCondition ref="B19:B46"/>
+  </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" xr:uid="{8D37ED2A-6F4C-4B2C-B212-84B5255111B4}"/>
-    <hyperlink ref="B12" r:id="rId2" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
-    <hyperlink ref="B11" r:id="rId3" xr:uid="{9848EFF2-7231-4687-A175-3EA385AD5EA8}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100156B981FAAFB4349A28B03AB4EEECF9F" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1e7c9bb6974a57a0073a8d48fc3b6089">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ea66b1c-fa60-4493-a86c-b420df37761a" xmlns:ns3="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5753863158ce54f5fdf0d8971fe3971" ns2:_="" ns3:_="">
-    <xsd:import namespace="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <xsd:import namespace="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006748505E66128D48AAED90CD5CD3616F" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b912ec8155dd4e933917767331a7e7b9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" xmlns:ns3="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f994fb40b965d01e7e08c4f92ceb61cd" ns2:_="" ns3:_="">
+    <xsd:import namespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <xsd:import namespace="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:note" minOccurs="0"/>
-                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:Date_x002f_Heure" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1032,36 +1409,68 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4ea66b1c-fa60-4493-a86c-b420df37761a" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="84381483-150a-4726-b180-307f5f59d12b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{517dfd69-ad1a-4b80-a735-177bb10dea14}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4ea66b1c-fa60-4493-a86c-b420df37761a">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4c7b0293-1299-401f-a92e-ea8ec6326420}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="13e36eaf-61a1-47aa-b343-0f7d626aa9a0">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -1071,93 +1480,6 @@
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="note" ma:index="20" nillable="true" ma:displayName="note" ma:format="Dropdown" ma:internalName="note">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="84381483-150a-4726-b180-307f5f59d12b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="24" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Date_x002f_Heure" ma:index="25" nillable="true" ma:displayName="Date/Heure" ma:format="DateTime" ma:internalName="Date_x002f_Heure">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="26" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1259,37 +1581,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="4ea66b1c-fa60-4493-a86c-b420df37761a" xsi:nil="true"/>
-    <Date_x002f_Heure xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0">
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <note xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AB3605-D74C-42B6-A2DD-9EBC41B913EF}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0C5E93-65BA-4187-9929-805FF0E80B6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <ds:schemaRef ds:uri="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -1300,21 +1619,13 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0610B8D-6EB9-4C25-8CE0-612AE3B494D1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <ds:schemaRef ds:uri="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/mobility-data-standard/mobility-data-standard.xlsx
+++ b/mobility-data-standard/mobility-data-standard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138286F2-E46E-4CF2-8C66-EDEB33A95618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE1E769-95E6-4340-8DC1-C8C9037B7252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -342,13 +342,16 @@
   </si>
   <si>
     <t>skos:Concept,https://w3id.org/mobilitydcatap#MobilityDataStandard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sara Guerra de Oliveira (University of Maribor) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +377,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -418,7 +436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -468,6 +486,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -777,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.7109375" customWidth="1"/>
@@ -852,17 +872,20 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
+      <c r="A8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>102</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
       </c>
       <c r="C9" s="1"/>
     </row>
@@ -874,106 +897,98 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B11)</f>
+      <c r="B13" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B12)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/1.2.0</v>
       </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B14" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B21" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="E21" t="s">
         <v>101</v>
@@ -981,43 +996,42 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B23)," ","-"),",",""))</f>
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B24)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/c-its</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C24" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B24)," ","-"),",",""),"ii","II"))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>101</v>
@@ -1025,28 +1039,29 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B25)," ","-"),",",""))</f>
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(B25)," ","-"),",",""),"ii","II"))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/datex-II</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B26)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/dino</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C26" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="E25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="E26" t="s">
         <v>101</v>
@@ -1054,13 +1069,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
         <v>101</v>
@@ -1068,28 +1083,27 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B29" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <f t="shared" ref="A29:A32" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B29)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
@@ -1097,14 +1111,14 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gml</v>
+        <f t="shared" ref="A30:A33" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B30)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gbfs</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="E30" t="s">
         <v>101</v>
@@ -1113,13 +1127,13 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gml</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
         <v>101</v>
@@ -1128,115 +1142,116 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/gtfs-rt</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C33" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E32" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C34" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="E34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B35" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C35" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B35)," ","-"),",",""))</f>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B36)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/netex</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C36" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E35" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B36)," ","-"),",",""))</f>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-o</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B37" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C37" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="E36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
+      <c r="E37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B38)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocit-c</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B38" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C38" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E37" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B38)," ","-"),",",""))</f>
+      <c r="E38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B39)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/ocpi</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>79</v>
       </c>
       <c r="E39" t="s">
         <v>101</v>
@@ -1244,13 +1259,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
         <v>101</v>
@@ -1258,13 +1273,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E41" t="s">
         <v>101</v>
@@ -1272,28 +1287,27 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B43" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="E42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B43)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="E43" t="s">
         <v>101</v>
@@ -1302,42 +1316,42 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B44)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/siri</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B45)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tn-its</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B45" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+      <c r="E45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B46" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C46" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="E45" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B46)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tpegml</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="E46" t="s">
         <v>101</v>
@@ -1346,25 +1360,40 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B47)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/tpegml</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B48)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-data-standard/other</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B48" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C48" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E48" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:C46">
-    <sortCondition ref="B19:B46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:C47">
+    <sortCondition ref="B20:B47"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
+    <hyperlink ref="B15" r:id="rId1" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
